--- a/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_gastroenterologica.xlsx
+++ b/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_gastroenterologica.xlsx
@@ -416,22 +416,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1108</t>
         </is>
       </c>
     </row>
@@ -443,22 +443,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.585 (49,3%)</t>
+          <t>1.599 (49,0%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>512 (47,9%)</t>
+          <t>524 (48,2%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>537 (48,2%)</t>
+          <t>530 (49,7%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>536 (51,9%)</t>
+          <t>545 (49,2%)</t>
         </is>
       </c>
     </row>
@@ -470,22 +470,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.075 (33,4%)</t>
+          <t>1.117 (34,2%)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>370 (34,6%)</t>
+          <t>377 (34,7%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>353 (31,7%)</t>
+          <t>384 (36,0%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>352 (34,1%)</t>
+          <t>356 (32,1%)</t>
         </is>
       </c>
     </row>
@@ -497,22 +497,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.053 (32,7%)</t>
+          <t>1.086 (33,3%)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>325 (30,4%)</t>
+          <t>358 (32,9%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>390 (35,0%)</t>
+          <t>346 (32,4%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>338 (32,7%)</t>
+          <t>382 (34,5%)</t>
         </is>
       </c>
     </row>
@@ -524,22 +524,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.088 (33,8%)</t>
+          <t>1.059 (32,5%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>373 (34,9%)</t>
+          <t>352 (32,4%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>372 (33,4%)</t>
+          <t>337 (31,6%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>343 (33,2%)</t>
+          <t>370 (33,4%)</t>
         </is>
       </c>
     </row>
@@ -551,22 +551,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>250 (7,8%)</t>
+          <t>2.192 (67,2%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>82 (7,7%)</t>
+          <t>732 (67,3%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>94 (8,4%)</t>
+          <t>726 (68,0%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>74 (7,2%)</t>
+          <t>734 (66,2%)</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A10BH 1.167 (36,3%)</t>
+          <t>B10AE54 229 (7,0%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A10BD07 411 (38,5%)</t>
+          <t>A10BD07 83 (7,6%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A10BD15 407 (36,5%)</t>
+          <t>J10BD19 83 (7,8%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A10BH 400 (38,7%)</t>
+          <t>A10BH02 87 (7,9%)</t>
         </is>
       </c>
     </row>
@@ -612,22 +612,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A10BD07 1.137 (35,4%)</t>
+          <t>J10BD19 221 (6,8%)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A10BH 395 (37,0%)</t>
+          <t>M10BD09 80 (7,4%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A10BK 406 (36,4%)</t>
+          <t>B10BX16 80 (7,5%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A10BD09 377 (36,5%)</t>
+          <t>M10BD16 84 (7,6%)</t>
         </is>
       </c>
     </row>
@@ -639,22 +639,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A10BD08 1.132 (35,2%)</t>
+          <t>A10BH02 215 (6,6%)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A10BD21 392 (36,7%)</t>
+          <t>B10AE54 80 (7,4%)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A10BD08 403 (36,1%)</t>
+          <t>C10BH02 79 (7,4%)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A10BD10 377 (36,5%)</t>
+          <t>M10BX16 83 (7,5%)</t>
         </is>
       </c>
     </row>
@@ -666,22 +666,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A10BD16 1.131 (35,2%)</t>
+          <t>J10BJ01 211 (6,5%)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A10BD16 389 (36,4%)</t>
+          <t>D10BD13 77 (7,1%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A10BD19 398 (35,7%)</t>
+          <t>B10BD16 78 (7,3%)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A10BD20 373 (36,1%)</t>
+          <t>B10BD20 82 (7,4%)</t>
         </is>
       </c>
     </row>
@@ -693,22 +693,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A10BD20 1.126 (35,0%)</t>
+          <t>A10BD07 208 (6,4%)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A10BD08 383 (35,9%)</t>
+          <t>M10BD21 77 (7,1%)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A10AE56 392 (35,2%)</t>
+          <t>C10BD21 74 (6,9%)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A10BD23 370 (35,8%)</t>
+          <t>C10BD23 80 (7,2%)</t>
         </is>
       </c>
     </row>
@@ -727,22 +727,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A10BD 3.192 (99,3%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD 12 (0,4%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A10BD 1.057 (99,0%)</t>
+          <t>A10BD C10BD D10BD J10BD M10BD 3 (0,3%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A10BD 1.113 (99,8%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD 5 (0,5%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A10BD 1.022 (98,9%)</t>
+          <t>A10BD B10BD C10BD J10BD M10BD 4 (0,4%)</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A10AE 1.594 (49,6%)</t>
+          <t>A10BD C10BD D10BD J10BD M10BD 10 (0,3%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A10AE 545 (51,0%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD 3 (0,3%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A10AE 557 (50,0%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD M10BD 5 (0,5%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A10AE 492 (47,6%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD 4 (0,4%)</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A10BH 971 (30,2%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD M10BD 9 (0,3%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A10BH 329 (30,8%)</t>
+          <t>A10BD B10BD C10BD J10BD J10JE 2 (0,2%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A10BK 342 (30,7%)</t>
+          <t>A10BD C10BD D10BD J10BD M10BD 4 (0,4%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A10BH 330 (31,9%)</t>
+          <t>A10BD B10BD C10BD D10BH J10BD M10BD 3 (0,3%)</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A10BK 943 (29,3%)</t>
+          <t>A10BD B10BD C10BD J10BD M10BD 8 (0,2%)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A10BJ 312 (29,2%)</t>
+          <t>A10BD B10BD C10BD D10BD M10BD 2 (0,2%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A10BJ 324 (29,1%)</t>
+          <t>A10BD B10BD C10BD J10BD M10BD 4 (0,4%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A10BX 307 (29,7%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD M10BD 3 (0,3%)</t>
         </is>
       </c>
     </row>
@@ -835,22 +835,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A10BJ 918 (28,5%)</t>
+          <t>A10BD B10BD C10BD D10BD M10BD 6 (0,2%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A10BK 297 (27,8%)</t>
+          <t>A10BD B10BD D10BD J10BD M10BD 2 (0,2%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A10BX 313 (28,1%)</t>
+          <t>A10BD B10BD C10BD D10BD M10BD 3 (0,3%)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>A10BK 304 (29,4%)</t>
+          <t>A10BD C10BD D10BD J10BD M10BD 3 (0,3%)</t>
         </is>
       </c>
     </row>

--- a/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_gastroenterologica.xlsx
+++ b/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_gastroenterologica.xlsx
@@ -585,22 +585,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B10AE54 229 (7,0%)</t>
+          <t>NA 229 (7,0%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A10BD07 83 (7,6%)</t>
+          <t>kk 83 (7,6%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>J10BD19 83 (7,8%)</t>
+          <t>NA 83 (7,8%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A10BH02 87 (7,9%)</t>
+          <t>NA 87 (7,9%)</t>
         </is>
       </c>
     </row>
@@ -612,22 +612,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J10BD19 221 (6,8%)</t>
+          <t>NA 221 (6,8%)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M10BD09 80 (7,4%)</t>
+          <t>NA 80 (7,4%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B10BX16 80 (7,5%)</t>
+          <t>NA 80 (7,5%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>M10BD16 84 (7,6%)</t>
+          <t>NA 84 (7,6%)</t>
         </is>
       </c>
     </row>
@@ -639,22 +639,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A10BH02 215 (6,6%)</t>
+          <t>NA 215 (6,6%)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B10AE54 80 (7,4%)</t>
+          <t>NA 80 (7,4%)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C10BH02 79 (7,4%)</t>
+          <t>NA 79 (7,4%)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>M10BX16 83 (7,5%)</t>
+          <t>NA 83 (7,5%)</t>
         </is>
       </c>
     </row>
@@ -666,22 +666,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>J10BJ01 211 (6,5%)</t>
+          <t>NA 211 (6,5%)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D10BD13 77 (7,1%)</t>
+          <t>NA 77 (7,1%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B10BD16 78 (7,3%)</t>
+          <t>NA 78 (7,3%)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B10BD20 82 (7,4%)</t>
+          <t>NA 82 (7,4%)</t>
         </is>
       </c>
     </row>
@@ -693,22 +693,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A10BD07 208 (6,4%)</t>
+          <t>kk 208 (6,4%)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M10BD21 77 (7,1%)</t>
+          <t>NA 77 (7,1%)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C10BD21 74 (6,9%)</t>
+          <t>NA 74 (6,9%)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C10BD23 80 (7,2%)</t>
+          <t>NA 80 (7,2%)</t>
         </is>
       </c>
     </row>
@@ -727,22 +727,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD 12 (0,4%)</t>
+          <t>e B10BD C10BD D10BD M10BD 186 (3,7%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A10BD C10BD D10BD J10BD M10BD 3 (0,3%)</t>
+          <t>e B10BD C10BD D10BD M10BD 62 (3,7%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD 5 (0,5%)</t>
+          <t>e B10BD C10BD D10BD M10BD 66 (4,1%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD J10BD M10BD 4 (0,4%)</t>
+          <t>e B10BD C10BD J10BD M10BD 71 (4,2%)</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A10BD C10BD D10BD J10BD M10BD 10 (0,3%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 178 (3,6%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD 3 (0,3%)</t>
+          <t>e B10BD C10BD D10BD J10BD 54 (3,2%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD M10BD 5 (0,5%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 62 (3,8%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD 4 (0,4%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 65 (3,8%)</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD M10BD 9 (0,3%)</t>
+          <t>e B10BD C10BD J10BD M10BD 175 (3,5%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD J10BD J10JE 2 (0,2%)</t>
+          <t>e B10BD C10BD J10BD M10BD 52 (3,1%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A10BD C10BD D10BD J10BD M10BD 4 (0,4%)</t>
+          <t>e B10BD C10BD D10BD J10BD 57 (3,5%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BH J10BD M10BD 3 (0,3%)</t>
+          <t>e B10BD C10BD D10BD J10BD 62 (3,7%)</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD J10BD M10BD 8 (0,2%)</t>
+          <t>e B10BD C10BD D10BD J10BD 173 (3,5%)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD M10BD 2 (0,2%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 51 (3,0%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD J10BD M10BD 4 (0,4%)</t>
+          <t>e C10BD D10BD J10BD M10BD 55 (3,4%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD M10BD 3 (0,3%)</t>
+          <t>e B10BD D10BD J10BD M10BD 59 (3,5%)</t>
         </is>
       </c>
     </row>
@@ -835,22 +835,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD M10BD 6 (0,2%)</t>
+          <t>e B10BD D10BD J10BD M10BD 162 (3,2%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A10BD B10BD D10BD J10BD M10BD 2 (0,2%)</t>
+          <t>e B10BD D10BD J10BD M10BD 50 (3,0%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD M10BD 3 (0,3%)</t>
+          <t>e B10BD D10BD J10BD M10BD 53 (3,3%)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>A10BD C10BD D10BD J10BD M10BD 3 (0,3%)</t>
+          <t>e B10BD C10BD D10BD M10BD 58 (3,4%)</t>
         </is>
       </c>
     </row>

--- a/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_gastroenterologica.xlsx
+++ b/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_gastroenterologica.xlsx
@@ -727,22 +727,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 186 (3,7%)</t>
+          <t>e B10BD C10BD D10BD M10BD 123 (3,8%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 62 (3,7%)</t>
+          <t>e B10BD C10BD D10BD M10BD 41 (3,8%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 66 (4,1%)</t>
+          <t>e B10BD C10BD D10BD M10BD 43 (4,0%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD J10BD M10BD 71 (4,2%)</t>
+          <t>e B10BD C10BD D10BD J10BD 46 (4,2%)</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 178 (3,6%)</t>
+          <t>e B10BD C10BD D10BD J10BD 122 (3,7%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 54 (3,2%)</t>
+          <t>e B10BD C10BD D10BD J10BD 38 (3,5%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 62 (3,8%)</t>
+          <t>e C10BD D10BD J10BD M10BD 43 (4,0%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 65 (3,8%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 43 (3,9%)</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD J10BD M10BD 175 (3,5%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 112 (3,4%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD J10BD M10BD 52 (3,1%)</t>
+          <t>e B10BD D10BD J10BD M10BD 30 (2,8%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 57 (3,5%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 41 (3,8%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 62 (3,7%)</t>
+          <t>e B10BD C10BD J10BD M10BD 41 (3,7%)</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 173 (3,5%)</t>
+          <t>e C10BD D10BD J10BD M10BD 105 (3,2%)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 51 (3,0%)</t>
+          <t>e C10BD D10BD J10BD M10BD 28 (2,6%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>e C10BD D10BD J10BD M10BD 55 (3,4%)</t>
+          <t>e B10BD C10BD D10BD J10BD 38 (3,6%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 59 (3,5%)</t>
+          <t>e B10BD C10BD D10BD M10BD 39 (3,5%)</t>
         </is>
       </c>
     </row>
@@ -835,22 +835,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 162 (3,2%)</t>
+          <t>e B10BD C10BD J10BD M10BD 102 (3,1%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 50 (3,0%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 28 (2,6%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 53 (3,3%)</t>
+          <t>e B10BD C10BD J10BD M10BD 36 (3,4%)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 58 (3,4%)</t>
+          <t>e B10BD D10BD J10BD M10BD 34 (3,1%)</t>
         </is>
       </c>
     </row>
